--- a/source_data.xlsx
+++ b/source_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alenka/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7745772-272B-574A-B72B-476939A4FF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786C1498-54E5-F24F-9F69-AB2E62025FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="20160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="20160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="locations" sheetId="7" r:id="rId1"/>
@@ -237,7 +237,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="89">
   <si>
     <t>distributor_zip</t>
   </si>
@@ -411,9 +411,6 @@
   </si>
   <si>
     <t>City of Industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coos Bay </t>
   </si>
   <si>
     <t>Laughlin</t>
@@ -959,28 +956,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -988,7 +985,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2">
         <v>15238</v>
@@ -1006,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -1014,7 +1011,7 @@
         <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3">
         <v>91789</v>
@@ -1032,15 +1029,15 @@
         <v>40000</v>
       </c>
       <c r="H3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" t="s">
         <v>70</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
       </c>
       <c r="C4">
         <v>97420</v>
@@ -1058,15 +1055,15 @@
         <v>40000</v>
       </c>
       <c r="H4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5">
         <v>89029</v>
@@ -1084,15 +1081,15 @@
         <v>40000</v>
       </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>83263</v>
@@ -1110,15 +1107,15 @@
         <v>40000</v>
       </c>
       <c r="H6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7">
         <v>86045</v>
@@ -1136,15 +1133,15 @@
         <v>40000</v>
       </c>
       <c r="H7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8">
         <v>95687</v>
@@ -1162,15 +1159,15 @@
         <v>40000</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9">
         <v>99362</v>
@@ -1188,7 +1185,7 @@
         <v>40000</v>
       </c>
       <c r="H9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1210,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="D1" s="1"/>
     </row>
@@ -1706,7 +1703,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -13405,10 +13402,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -13902,7 +13899,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -14859,7 +14856,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B88" s="2">
         <v>59019</v>
@@ -14870,7 +14867,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B89" s="2">
         <v>59634</v>
@@ -14881,7 +14878,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B90" s="2">
         <v>59808</v>
@@ -14892,7 +14889,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B91" s="2">
         <v>81321</v>
@@ -14903,7 +14900,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B92" s="2">
         <v>81416</v>
@@ -14914,7 +14911,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B93" s="2">
         <v>81504</v>
@@ -14925,7 +14922,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B94" s="2">
         <v>81650</v>
@@ -14936,7 +14933,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B95" s="2">
         <v>83014</v>
@@ -14947,7 +14944,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B96" s="2">
         <v>83338</v>
@@ -14958,7 +14955,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B97" s="2">
         <v>83544</v>
@@ -14969,7 +14966,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B98" s="2">
         <v>83638</v>
@@ -14980,7 +14977,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B99" s="2">
         <v>83706</v>
@@ -14991,7 +14988,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B100" s="2">
         <v>84003</v>
@@ -15002,7 +14999,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B101" s="2">
         <v>84414</v>
@@ -15013,7 +15010,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B102" s="2">
         <v>84532</v>
@@ -15024,7 +15021,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B103" s="2">
         <v>84780</v>
@@ -15035,7 +15032,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B104" s="2">
         <v>85012</v>
@@ -15046,7 +15043,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B105" s="2">
         <v>86004</v>
@@ -15057,7 +15054,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B106" s="2">
         <v>86042</v>
@@ -15068,7 +15065,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B107" s="2">
         <v>86314</v>
@@ -15079,7 +15076,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B108" s="2">
         <v>86426</v>
@@ -15090,7 +15087,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B109" s="2">
         <v>89104</v>
@@ -15101,7 +15098,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B110" s="2">
         <v>89408</v>
@@ -15112,7 +15109,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B111" s="2">
         <v>89509</v>
@@ -15123,7 +15120,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B112" s="2">
         <v>89822</v>
@@ -15134,7 +15131,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B113" s="2">
         <v>90061</v>
@@ -15145,7 +15142,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B114" s="2">
         <v>93030</v>
@@ -15156,7 +15153,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B115" s="2">
         <v>93427</v>
@@ -15167,7 +15164,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B116" s="2">
         <v>93703</v>
@@ -15178,7 +15175,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B117" s="2">
         <v>93906</v>
@@ -15189,7 +15186,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B118" s="2">
         <v>94403</v>
@@ -15200,7 +15197,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B119" s="2">
         <v>95051</v>
@@ -15211,7 +15208,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B120" s="2">
         <v>95993</v>
@@ -15222,7 +15219,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B121" s="2">
         <v>96130</v>
@@ -15233,7 +15230,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B122" s="2">
         <v>97002</v>
@@ -15244,7 +15241,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B123" s="2">
         <v>97524</v>
@@ -15255,7 +15252,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B124" s="2">
         <v>97862</v>
@@ -15266,7 +15263,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B125" s="2">
         <v>97920</v>
@@ -15277,7 +15274,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B126" s="2">
         <v>98059</v>
@@ -15288,7 +15285,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B127" s="2">
         <v>98248</v>
@@ -15299,7 +15296,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B128" s="2">
         <v>98812</v>
@@ -15310,7 +15307,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B129" s="2">
         <v>99223</v>
@@ -15321,7 +15318,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B130" s="2">
         <v>99350</v>
@@ -15332,7 +15329,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B131" s="2">
         <v>59019</v>
@@ -15343,7 +15340,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B132" s="2">
         <v>59634</v>
@@ -15354,7 +15351,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B133" s="2">
         <v>59808</v>
@@ -15365,7 +15362,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B134" s="2">
         <v>81321</v>
@@ -15376,7 +15373,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B135" s="2">
         <v>81416</v>
@@ -15387,7 +15384,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B136" s="2">
         <v>81504</v>
@@ -15398,7 +15395,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B137" s="2">
         <v>81650</v>
@@ -15409,7 +15406,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B138" s="2">
         <v>83014</v>
@@ -15420,7 +15417,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B139" s="2">
         <v>83338</v>
@@ -15431,7 +15428,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B140" s="2">
         <v>83544</v>
@@ -15442,7 +15439,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B141" s="2">
         <v>83638</v>
@@ -15453,7 +15450,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B142" s="2">
         <v>83706</v>
@@ -15464,7 +15461,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B143" s="2">
         <v>84003</v>
@@ -15475,7 +15472,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B144" s="2">
         <v>84414</v>
@@ -15486,7 +15483,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B145" s="2">
         <v>84532</v>
@@ -15497,7 +15494,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B146" s="2">
         <v>84780</v>
@@ -15508,7 +15505,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B147" s="2">
         <v>85012</v>
@@ -15519,7 +15516,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B148" s="2">
         <v>86004</v>
@@ -15530,7 +15527,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B149" s="2">
         <v>86042</v>
@@ -15541,7 +15538,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B150" s="2">
         <v>86314</v>
@@ -15552,7 +15549,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B151" s="2">
         <v>86426</v>
@@ -15563,7 +15560,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B152" s="2">
         <v>89104</v>
@@ -15574,7 +15571,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B153" s="2">
         <v>89408</v>
@@ -15585,7 +15582,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B154" s="2">
         <v>89509</v>
@@ -15596,7 +15593,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B155" s="2">
         <v>89822</v>
@@ -15607,7 +15604,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B156" s="2">
         <v>90061</v>
@@ -15618,7 +15615,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B157" s="2">
         <v>93030</v>
@@ -15629,7 +15626,7 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B158" s="2">
         <v>93427</v>
@@ -15640,7 +15637,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B159" s="2">
         <v>93703</v>
@@ -15651,7 +15648,7 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B160" s="2">
         <v>93906</v>
@@ -15662,7 +15659,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B161" s="2">
         <v>94403</v>
@@ -15673,7 +15670,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B162" s="2">
         <v>95051</v>
@@ -15684,7 +15681,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B163" s="2">
         <v>95993</v>
@@ -15695,7 +15692,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B164" s="2">
         <v>96130</v>
@@ -15706,7 +15703,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B165" s="2">
         <v>97002</v>
@@ -15717,7 +15714,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B166" s="2">
         <v>97524</v>
@@ -15728,7 +15725,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B167" s="2">
         <v>97862</v>
@@ -15739,7 +15736,7 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B168" s="2">
         <v>97920</v>
@@ -15750,7 +15747,7 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B169" s="2">
         <v>98059</v>
@@ -15761,7 +15758,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B170" s="2">
         <v>98248</v>
@@ -15772,7 +15769,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B171" s="2">
         <v>98812</v>
@@ -15783,7 +15780,7 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B172" s="2">
         <v>99223</v>
@@ -15794,7 +15791,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B173" s="2">
         <v>99350</v>
@@ -15805,7 +15802,7 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B174" s="2">
         <v>59019</v>
@@ -15816,7 +15813,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B175" s="2">
         <v>59634</v>
@@ -15827,7 +15824,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B176" s="2">
         <v>59808</v>
@@ -15838,7 +15835,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B177" s="2">
         <v>81321</v>
@@ -15849,7 +15846,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B178" s="2">
         <v>81416</v>
@@ -15860,7 +15857,7 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B179" s="2">
         <v>81504</v>
@@ -15871,7 +15868,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B180" s="2">
         <v>81650</v>
@@ -15882,7 +15879,7 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B181" s="2">
         <v>83014</v>
@@ -15893,7 +15890,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B182" s="2">
         <v>83338</v>
@@ -15904,7 +15901,7 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B183" s="2">
         <v>83544</v>
@@ -15915,7 +15912,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B184" s="2">
         <v>83638</v>
@@ -15926,7 +15923,7 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B185" s="2">
         <v>83706</v>
@@ -15937,7 +15934,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B186" s="2">
         <v>84003</v>
@@ -15948,7 +15945,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B187" s="2">
         <v>84414</v>
@@ -15959,7 +15956,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B188" s="2">
         <v>84532</v>
@@ -15970,7 +15967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B189" s="2">
         <v>84780</v>
@@ -15981,7 +15978,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B190" s="2">
         <v>85012</v>
@@ -15992,7 +15989,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B191" s="2">
         <v>86004</v>
@@ -16003,7 +16000,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B192" s="2">
         <v>86042</v>
@@ -16014,7 +16011,7 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B193" s="2">
         <v>86314</v>
@@ -16025,7 +16022,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B194" s="2">
         <v>86426</v>
@@ -16036,7 +16033,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B195" s="2">
         <v>89104</v>
@@ -16047,7 +16044,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B196" s="2">
         <v>89408</v>
@@ -16058,7 +16055,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B197" s="2">
         <v>89509</v>
@@ -16069,7 +16066,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B198" s="2">
         <v>89822</v>
@@ -16080,7 +16077,7 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B199" s="2">
         <v>90061</v>
@@ -16091,7 +16088,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B200" s="2">
         <v>93030</v>
@@ -16102,7 +16099,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B201" s="2">
         <v>93427</v>
@@ -16113,7 +16110,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B202" s="2">
         <v>93703</v>
@@ -16124,7 +16121,7 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B203" s="2">
         <v>93906</v>
@@ -16135,7 +16132,7 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B204" s="2">
         <v>94403</v>
@@ -16146,7 +16143,7 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B205" s="2">
         <v>95051</v>
@@ -16157,7 +16154,7 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B206" s="2">
         <v>95993</v>
@@ -16168,7 +16165,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B207" s="2">
         <v>96130</v>
@@ -16179,7 +16176,7 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B208" s="2">
         <v>97002</v>
@@ -16190,7 +16187,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B209" s="2">
         <v>97524</v>
@@ -16201,7 +16198,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B210" s="2">
         <v>97862</v>
@@ -16212,7 +16209,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B211" s="2">
         <v>97920</v>
@@ -16223,7 +16220,7 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B212" s="2">
         <v>98059</v>
@@ -16234,7 +16231,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B213" s="2">
         <v>98248</v>
@@ -16245,7 +16242,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B214" s="2">
         <v>98812</v>
@@ -16256,7 +16253,7 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B215" s="2">
         <v>99223</v>
@@ -16267,7 +16264,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B216" s="2">
         <v>99350</v>
@@ -16278,7 +16275,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B217" s="2">
         <v>59019</v>
@@ -16289,7 +16286,7 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B218" s="2">
         <v>59634</v>
@@ -16300,7 +16297,7 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B219" s="2">
         <v>59808</v>
@@ -16311,7 +16308,7 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B220" s="2">
         <v>81321</v>
@@ -16322,7 +16319,7 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B221" s="2">
         <v>81416</v>
@@ -16333,7 +16330,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B222" s="2">
         <v>81504</v>
@@ -16344,7 +16341,7 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B223" s="2">
         <v>81650</v>
@@ -16355,7 +16352,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B224" s="2">
         <v>83014</v>
@@ -16366,7 +16363,7 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B225" s="2">
         <v>83338</v>
@@ -16377,7 +16374,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B226" s="2">
         <v>83544</v>
@@ -16388,7 +16385,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B227" s="2">
         <v>83638</v>
@@ -16399,7 +16396,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B228" s="2">
         <v>83706</v>
@@ -16410,7 +16407,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B229" s="2">
         <v>84003</v>
@@ -16421,7 +16418,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B230" s="2">
         <v>84414</v>
@@ -16432,7 +16429,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B231" s="2">
         <v>84532</v>
@@ -16443,7 +16440,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B232" s="2">
         <v>84780</v>
@@ -16454,7 +16451,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B233" s="2">
         <v>85012</v>
@@ -16465,7 +16462,7 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B234" s="2">
         <v>86004</v>
@@ -16476,7 +16473,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B235" s="2">
         <v>86042</v>
@@ -16487,7 +16484,7 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B236" s="2">
         <v>86314</v>
@@ -16498,7 +16495,7 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B237" s="2">
         <v>86426</v>
@@ -16509,7 +16506,7 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B238" s="2">
         <v>89104</v>
@@ -16520,7 +16517,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B239" s="2">
         <v>89408</v>
@@ -16531,7 +16528,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B240" s="2">
         <v>89509</v>
@@ -16542,7 +16539,7 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B241" s="2">
         <v>89822</v>
@@ -16553,7 +16550,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B242" s="2">
         <v>90061</v>
@@ -16564,7 +16561,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B243" s="2">
         <v>93030</v>
@@ -16575,7 +16572,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B244" s="2">
         <v>93427</v>
@@ -16586,7 +16583,7 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B245" s="2">
         <v>93703</v>
@@ -16597,7 +16594,7 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B246" s="2">
         <v>93906</v>
@@ -16608,7 +16605,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B247" s="2">
         <v>94403</v>
@@ -16619,7 +16616,7 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B248" s="2">
         <v>95051</v>
@@ -16630,7 +16627,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B249" s="2">
         <v>95993</v>
@@ -16641,7 +16638,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B250" s="2">
         <v>96130</v>
@@ -16652,7 +16649,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B251" s="2">
         <v>97002</v>
@@ -16663,7 +16660,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B252" s="2">
         <v>97524</v>
@@ -16674,7 +16671,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B253" s="2">
         <v>97862</v>
@@ -16685,7 +16682,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B254" s="2">
         <v>97920</v>
@@ -16696,7 +16693,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B255" s="2">
         <v>98059</v>
@@ -16707,7 +16704,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B256" s="2">
         <v>98248</v>
@@ -16718,7 +16715,7 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B257" s="2">
         <v>98812</v>
@@ -16729,7 +16726,7 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B258" s="2">
         <v>99223</v>
@@ -16740,7 +16737,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B259" s="2">
         <v>99350</v>
@@ -16751,7 +16748,7 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B260" s="2">
         <v>59019</v>
@@ -16762,7 +16759,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B261" s="2">
         <v>59634</v>
@@ -16773,7 +16770,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B262" s="2">
         <v>59808</v>
@@ -16784,7 +16781,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B263" s="2">
         <v>81321</v>
@@ -16795,7 +16792,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B264" s="2">
         <v>81416</v>
@@ -16806,7 +16803,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B265" s="2">
         <v>81504</v>
@@ -16817,7 +16814,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B266" s="2">
         <v>81650</v>
@@ -16828,7 +16825,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B267" s="2">
         <v>83014</v>
@@ -16839,7 +16836,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B268" s="2">
         <v>83338</v>
@@ -16850,7 +16847,7 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B269" s="2">
         <v>83544</v>
@@ -16861,7 +16858,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B270" s="2">
         <v>83638</v>
@@ -16872,7 +16869,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B271" s="2">
         <v>83706</v>
@@ -16883,7 +16880,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B272" s="2">
         <v>84003</v>
@@ -16894,7 +16891,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B273" s="2">
         <v>84414</v>
@@ -16905,7 +16902,7 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B274" s="2">
         <v>84532</v>
@@ -16916,7 +16913,7 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B275" s="2">
         <v>84780</v>
@@ -16927,7 +16924,7 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B276" s="2">
         <v>85012</v>
@@ -16938,7 +16935,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B277" s="2">
         <v>86004</v>
@@ -16949,7 +16946,7 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B278" s="2">
         <v>86042</v>
@@ -16960,7 +16957,7 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B279" s="2">
         <v>86314</v>
@@ -16971,7 +16968,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B280" s="2">
         <v>86426</v>
@@ -16982,7 +16979,7 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B281" s="2">
         <v>89104</v>
@@ -16993,7 +16990,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B282" s="2">
         <v>89408</v>
@@ -17004,7 +17001,7 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B283" s="2">
         <v>89509</v>
@@ -17015,7 +17012,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B284" s="2">
         <v>89822</v>
@@ -17026,7 +17023,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B285" s="2">
         <v>90061</v>
@@ -17037,7 +17034,7 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B286" s="2">
         <v>93030</v>
@@ -17048,7 +17045,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B287" s="2">
         <v>93427</v>
@@ -17059,7 +17056,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B288" s="2">
         <v>93703</v>
@@ -17070,7 +17067,7 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B289" s="2">
         <v>93906</v>
@@ -17081,7 +17078,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B290" s="2">
         <v>94403</v>
@@ -17092,7 +17089,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B291" s="2">
         <v>95051</v>
@@ -17103,7 +17100,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B292" s="2">
         <v>95993</v>
@@ -17114,7 +17111,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B293" s="2">
         <v>96130</v>
@@ -17125,7 +17122,7 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B294" s="2">
         <v>97002</v>
@@ -17136,7 +17133,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B295" s="2">
         <v>97524</v>
@@ -17147,7 +17144,7 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B296" s="2">
         <v>97862</v>
@@ -17158,7 +17155,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B297" s="2">
         <v>97920</v>
@@ -17169,7 +17166,7 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B298" s="2">
         <v>98059</v>
@@ -17180,7 +17177,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B299" s="2">
         <v>98248</v>
@@ -17191,7 +17188,7 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B300" s="2">
         <v>98812</v>
@@ -17202,7 +17199,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B301" s="2">
         <v>99223</v>
@@ -17213,7 +17210,7 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B302" s="2">
         <v>99350</v>
@@ -17224,7 +17221,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B303" s="2">
         <v>59019</v>
@@ -17235,7 +17232,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B304" s="2">
         <v>59634</v>
@@ -17246,7 +17243,7 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B305" s="2">
         <v>59808</v>
@@ -17257,7 +17254,7 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B306" s="2">
         <v>81321</v>
@@ -17268,7 +17265,7 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B307" s="2">
         <v>81416</v>
@@ -17279,7 +17276,7 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B308" s="2">
         <v>81504</v>
@@ -17290,7 +17287,7 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B309" s="2">
         <v>81650</v>
@@ -17301,7 +17298,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B310" s="2">
         <v>83014</v>
@@ -17312,7 +17309,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B311" s="2">
         <v>83338</v>
@@ -17323,7 +17320,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B312" s="2">
         <v>83544</v>
@@ -17334,7 +17331,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B313" s="2">
         <v>83638</v>
@@ -17345,7 +17342,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B314" s="2">
         <v>83706</v>
@@ -17356,7 +17353,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B315" s="2">
         <v>84003</v>
@@ -17367,7 +17364,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B316" s="2">
         <v>84414</v>
@@ -17378,7 +17375,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B317" s="2">
         <v>84532</v>
@@ -17389,7 +17386,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B318" s="2">
         <v>84780</v>
@@ -17400,7 +17397,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B319" s="2">
         <v>85012</v>
@@ -17411,7 +17408,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B320" s="2">
         <v>86004</v>
@@ -17422,7 +17419,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B321" s="2">
         <v>86042</v>
@@ -17433,7 +17430,7 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B322" s="2">
         <v>86314</v>
@@ -17444,7 +17441,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B323" s="2">
         <v>86426</v>
@@ -17455,7 +17452,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A324" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B324" s="2">
         <v>89104</v>
@@ -17466,7 +17463,7 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B325" s="2">
         <v>89408</v>
@@ -17477,7 +17474,7 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A326" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B326" s="2">
         <v>89509</v>
@@ -17488,7 +17485,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A327" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B327" s="2">
         <v>89822</v>
@@ -17499,7 +17496,7 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B328" s="2">
         <v>90061</v>
@@ -17510,7 +17507,7 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B329" s="2">
         <v>93030</v>
@@ -17521,7 +17518,7 @@
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B330" s="2">
         <v>93427</v>
@@ -17532,7 +17529,7 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B331" s="2">
         <v>93703</v>
@@ -17543,7 +17540,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B332" s="2">
         <v>93906</v>
@@ -17554,7 +17551,7 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B333" s="2">
         <v>94403</v>
@@ -17565,7 +17562,7 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B334" s="2">
         <v>95051</v>
@@ -17576,7 +17573,7 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B335" s="2">
         <v>95993</v>
@@ -17587,7 +17584,7 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B336" s="2">
         <v>96130</v>
@@ -17598,7 +17595,7 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B337" s="2">
         <v>97002</v>
@@ -17609,7 +17606,7 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B338" s="2">
         <v>97524</v>
@@ -17620,7 +17617,7 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B339" s="2">
         <v>97862</v>
@@ -17631,7 +17628,7 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B340" s="2">
         <v>97920</v>
@@ -17642,7 +17639,7 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B341" s="2">
         <v>98059</v>
@@ -17653,7 +17650,7 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A342" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B342" s="2">
         <v>98248</v>
@@ -17664,7 +17661,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B343" s="2">
         <v>98812</v>
@@ -17675,7 +17672,7 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B344" s="2">
         <v>99223</v>
@@ -17686,7 +17683,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B345" s="2">
         <v>99350</v>
@@ -17716,10 +17713,10 @@
         <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -17820,10 +17817,10 @@
         <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
